--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7415289-6D48-4FEC-94FA-1392872926D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A5E344-B76C-47D5-8B37-A9AFB59599AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28725" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23460" yWindow="2745" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -301,6 +301,18 @@
   <si>
     <t>109,0,112;112,0,109</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以建造的单位列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateUnitIDList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -411,7 +423,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -453,6 +465,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
@@ -733,11 +751,12 @@
     <col min="9" max="9" width="19.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.625" customWidth="1"/>
-    <col min="13" max="13" width="19.25" customWidth="1"/>
+    <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.625" customWidth="1"/>
+    <col min="14" max="14" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -772,13 +791,16 @@
         <v>34</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -812,14 +834,17 @@
       <c r="K2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -853,14 +878,17 @@
       <c r="K3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -894,12 +922,13 @@
       <c r="K4" s="6">
         <v>0</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -933,12 +962,13 @@
       <c r="K5" s="6">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -972,14 +1002,15 @@
       <c r="K6" s="6">
         <v>5</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1013,14 +1044,15 @@
       <c r="K7" s="6">
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="2"/>
+      <c r="M7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1054,14 +1086,17 @@
       <c r="K8" s="4">
         <v>5</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="15">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1095,14 +1130,17 @@
       <c r="K9" s="6">
         <v>10</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1136,10 +1174,11 @@
       <c r="K10" s="6">
         <v>0</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="2"/>
+      <c r="M10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>45</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A5E344-B76C-47D5-8B37-A9AFB59599AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7B2B31-D9CA-4284-AC01-D53EE92EF258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23460" yWindow="2745" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="1965" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -54,9 +54,6 @@
     <t>主基地</t>
   </si>
   <si>
-    <t>金矿</t>
-  </si>
-  <si>
     <t>采矿场</t>
   </si>
   <si>
@@ -188,10 +185,6 @@
   </si>
   <si>
     <t>描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可采集附近的矿源</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -312,6 +305,18 @@
   </si>
   <si>
     <t>CreateUnitIDList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>金钱的来源</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>油田</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>炼油厂</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -764,84 +769,84 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="120" x14ac:dyDescent="0.25">
@@ -849,43 +854,43 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -899,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="6">
         <v>5</v>
@@ -939,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
@@ -963,8 +968,8 @@
         <v>0</v>
       </c>
       <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>6</v>
+      <c r="M5" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -979,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="6">
         <v>5</v>
@@ -1003,11 +1008,11 @@
         <v>5</v>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>41</v>
+      <c r="M6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1021,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="6">
         <v>5</v>
@@ -1036,7 +1041,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J7" s="6">
         <v>500</v>
@@ -1046,10 +1051,10 @@
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1063,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="4">
         <v>5</v>
@@ -1078,7 +1083,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4">
         <v>1000</v>
@@ -1090,10 +1095,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1107,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="6">
         <v>5</v>
@@ -1122,7 +1127,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J9" s="6">
         <v>2000</v>
@@ -1131,13 +1136,13 @@
         <v>10</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1151,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
@@ -1176,10 +1181,10 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1207,27 +1212,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -1236,7 +1241,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>2</v>
@@ -1245,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="120" x14ac:dyDescent="0.25">
@@ -1253,22 +1258,22 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1285,10 +1290,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
@@ -1308,10 +1313,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
@@ -1331,10 +1336,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
@@ -1354,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7" s="8">
         <v>1</v>
@@ -1377,10 +1382,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
@@ -1400,10 +1405,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
@@ -1423,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="6">
         <v>1</v>
@@ -1446,10 +1451,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
@@ -1469,10 +1474,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12" s="6">
         <v>1</v>
@@ -1492,10 +1497,10 @@
         <v>2</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="6">
         <v>0</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7B2B31-D9CA-4284-AC01-D53EE92EF258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18A1297-D595-4B52-9859-3D606442A591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2880" yWindow="1965" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -189,14 +189,6 @@
   </si>
   <si>
     <t>为基地提供电力支持</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可训练步兵单位</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可生产装甲单位</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -316,7 +308,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>炼油厂</t>
+    <t>油井</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>碉堡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可生产坦克单位</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可生产步兵单位</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -796,10 +800,10 @@
         <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>38</v>
@@ -854,7 +858,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>37</v>
@@ -884,10 +888,10 @@
         <v>35</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>39</v>
@@ -969,7 +973,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -1009,10 +1013,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1086,7 +1090,7 @@
         <v>4</v>
       </c>
       <c r="J8" s="4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K8" s="4">
         <v>5</v>
@@ -1097,8 +1101,8 @@
       <c r="M8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>41</v>
+      <c r="N8" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1136,13 +1140,13 @@
         <v>10</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>42</v>
+      <c r="N9" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1181,10 +1185,10 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1212,22 +1216,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>48</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
@@ -1258,22 +1262,22 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1290,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>6</v>
@@ -1313,7 +1317,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>7</v>
@@ -1336,10 +1340,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
@@ -1359,10 +1363,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7" s="8">
         <v>1</v>
@@ -1382,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>29</v>
@@ -1405,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>6</v>
@@ -1428,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>7</v>
@@ -1451,10 +1455,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
@@ -1474,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12" s="6">
         <v>1</v>
@@ -1497,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>29</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18A1297-D595-4B52-9859-3D606442A591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0874920-234B-437C-A4CB-C4483A2B71D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="1965" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9630" yWindow="2685" windowWidth="34440" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -280,10 +280,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>12,0,15;15,0,12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>109,0,112;112,0,109</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -321,6 +317,10 @@
   </si>
   <si>
     <t>可生产步兵单位</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12,0,18;18,0,12</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -800,7 +800,7 @@
         <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>42</v>
@@ -888,7 +888,7 @@
         <v>35</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>43</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -1013,10 +1013,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1102,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1140,13 +1140,13 @@
         <v>10</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>41</v>
@@ -1386,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>29</v>
@@ -1501,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>29</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0874920-234B-437C-A4CB-C4483A2B71D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7F8A20-E2C2-4041-9E2B-AE47A5AB5007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9630" yWindow="2685" windowWidth="34440" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3690" windowWidth="34440" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -225,10 +225,6 @@
     <t>阵营</t>
   </si>
   <si>
-    <t>10,0,5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>兵营</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -263,10 +259,6 @@
   <si>
     <t>是否启用</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,0,10;5,0,15</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>建筑类型：
@@ -320,7 +312,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>12,0,18;18,0,12</t>
+    <t>5,0,15;5,0,25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,0,5</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0,22;22,0,15;10,0,30;30,0,10;10,0,10</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -341,17 +341,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -432,7 +435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -480,6 +483,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -800,7 +806,7 @@
         <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>42</v>
@@ -858,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>37</v>
@@ -888,7 +894,7 @@
         <v>35</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>43</v>
@@ -973,7 +979,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -1013,10 +1019,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1102,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1140,13 +1146,13 @@
         <v>10</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1185,7 +1191,7 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>41</v>
@@ -1216,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1231,7 +1237,7 @@
         <v>42</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
@@ -1265,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>45</v>
@@ -1277,7 +1283,7 @@
         <v>43</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1316,8 +1322,8 @@
       <c r="D5" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>61</v>
+      <c r="E5" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>7</v>
@@ -1339,11 +1345,11 @@
       <c r="D6" s="7">
         <v>1</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
@@ -1362,17 +1368,17 @@
       <c r="D7" s="7">
         <v>1</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="G7" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1383,9 +1389,9 @@
         <v>7</v>
       </c>
       <c r="D8" s="7">
-        <v>2</v>
-      </c>
-      <c r="E8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>73</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -1409,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>6</v>
@@ -1432,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>7</v>
@@ -1455,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
@@ -1478,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12" s="6">
         <v>1</v>
@@ -1501,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>29</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7F8A20-E2C2-4041-9E2B-AE47A5AB5007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CA8D27-A8B0-4963-8BC6-6339E5457EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3690" windowWidth="34440" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21045" yWindow="4065" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -920,7 +920,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="6">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CA8D27-A8B0-4963-8BC6-6339E5457EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC6AAB3-796E-496B-B562-496AEC2A0C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21045" yWindow="4065" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17160" yWindow="3180" windowWidth="24975" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -226,10 +226,6 @@
   </si>
   <si>
     <t>兵营</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,0,5</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -312,16 +308,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>5,0,15;5,0,25</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>25,0,5</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>15,0,22;22,0,15;10,0,30;30,0,10;10,0,10</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>主基地</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0,15</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,0,25</t>
+  </si>
+  <si>
+    <t>5,0,15;15,0,5</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -381,7 +388,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,6 +398,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +448,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -466,15 +479,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -485,6 +492,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -806,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>42</v>
@@ -864,7 +883,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>37</v>
@@ -894,7 +913,7 @@
         <v>35</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>43</v>
@@ -979,7 +998,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -1019,10 +1038,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1101,14 +1120,14 @@
       <c r="K8" s="4">
         <v>5</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="13">
         <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1145,14 +1164,14 @@
       <c r="K9" s="6">
         <v>10</v>
       </c>
-      <c r="L9" s="14" t="s">
-        <v>63</v>
+      <c r="L9" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1191,7 +1210,7 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>41</v>
@@ -1206,14 +1225,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EAF20F-3871-496D-B5D3-5055E4F35A32}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1222,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1237,7 +1256,7 @@
         <v>42</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
@@ -1271,7 +1290,7 @@
         <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>45</v>
@@ -1283,7 +1302,7 @@
         <v>43</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1299,7 +1318,7 @@
       <c r="D4" s="7">
         <v>1</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>48</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -1322,8 +1341,8 @@
       <c r="D5" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="16" t="s">
-        <v>71</v>
+      <c r="E5" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>7</v>
@@ -1345,8 +1364,8 @@
       <c r="D6" s="7">
         <v>1</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>51</v>
+      <c r="E6" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>50</v>
@@ -1368,11 +1387,11 @@
       <c r="D7" s="7">
         <v>1</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>72</v>
+      <c r="E7" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="8">
         <v>1</v>
@@ -1391,8 +1410,8 @@
       <c r="D8" s="7">
         <v>5</v>
       </c>
-      <c r="E8" s="16" t="s">
-        <v>73</v>
+      <c r="E8" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>29</v>
@@ -1402,117 +1421,140 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
+        <v>100</v>
+      </c>
+      <c r="B10" s="16">
         <v>2</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="16">
         <v>3</v>
       </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D10" s="15">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
+        <v>101</v>
+      </c>
+      <c r="B11" s="16">
+        <v>2</v>
+      </c>
+      <c r="C11" s="16">
+        <v>4</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F11" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15">
+        <v>102</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
+        <v>103</v>
+      </c>
+      <c r="B13" s="16">
+        <v>2</v>
+      </c>
+      <c r="C13" s="16">
         <v>6</v>
       </c>
-      <c r="G9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="D13" s="15">
+        <v>1</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
+        <v>104</v>
+      </c>
+      <c r="B14" s="16">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
+      <c r="D14" s="15">
         <v>2</v>
       </c>
-      <c r="C10" s="6">
-        <v>4</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6">
-        <v>2</v>
-      </c>
-      <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>10</v>
-      </c>
-      <c r="B13" s="6">
-        <v>2</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="E14" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G14" s="16">
         <v>0</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC6AAB3-796E-496B-B562-496AEC2A0C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF31E11-C24E-4B80-9BE6-E75A7A39C120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17160" yWindow="3180" windowWidth="24975" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2220" windowWidth="19995" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -312,10 +312,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>15,0,22;22,0,15;10,0,30;30,0,10;10,0,10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>主基地</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -329,6 +325,10 @@
   <si>
     <t>5,0,15;15,0,5</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,20;10,0,20;20,0,10;10,0,10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="6">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
@@ -1342,7 +1342,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>7</v>
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>50</v>
@@ -1408,10 +1408,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>29</v>
@@ -1434,10 +1434,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF31E11-C24E-4B80-9BE6-E75A7A39C120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EF307C-1311-4A9C-9E1A-2040B03E9272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2220" windowWidth="19995" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="4140" windowWidth="19995" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -54,9 +54,6 @@
     <t>主基地</t>
   </si>
   <si>
-    <t>采矿场</t>
-  </si>
-  <si>
     <t>电厂</t>
   </si>
   <si>
@@ -77,10 +74,6 @@
   </si>
   <si>
     <t>MainBase</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OilField</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -328,6 +321,46 @@
   </si>
   <si>
     <t>20,0,20;10,0,20;20,0,10;10,0,10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OilField</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Stope</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/PowerPlant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Barracks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/VehicleFactory</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Tower</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>油井</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/MainBase</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -388,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,12 +431,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,7 +475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -494,17 +521,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,84 +816,84 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="120" x14ac:dyDescent="0.25">
@@ -883,43 +901,43 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="M3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -933,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="6">
         <v>5</v>
@@ -972,8 +990,8 @@
       <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
+      <c r="D5" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
@@ -998,7 +1016,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -1012,8 +1030,8 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>14</v>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="E6" s="6">
         <v>5</v>
@@ -1038,10 +1056,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1054,8 +1072,8 @@
       <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>15</v>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E7" s="6">
         <v>5</v>
@@ -1080,10 +1098,10 @@
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1096,8 +1114,8 @@
       <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>27</v>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E8" s="4">
         <v>5</v>
@@ -1124,10 +1142,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1140,8 +1158,8 @@
       <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>16</v>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="E9" s="6">
         <v>5</v>
@@ -1165,13 +1183,13 @@
         <v>10</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1184,8 +1202,8 @@
       <c r="C10" s="2">
         <v>0</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>28</v>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
@@ -1210,10 +1228,10 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1225,43 +1243,47 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EAF20F-3871-496D-B5D3-5055E4F35A32}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.75" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -1269,45 +1291,51 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="H2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
@@ -1315,22 +1343,25 @@
       <c r="C4" s="8">
         <v>3</v>
       </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
@@ -1338,22 +1369,25 @@
       <c r="C5" s="8">
         <v>4</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B6" s="8">
         <v>1</v>
@@ -1361,22 +1395,25 @@
       <c r="C6" s="8">
         <v>5</v>
       </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
@@ -1384,22 +1421,25 @@
       <c r="C7" s="8">
         <v>6</v>
       </c>
-      <c r="D7" s="7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B8" s="8">
         <v>1</v>
@@ -1407,155 +1447,202 @@
       <c r="C8" s="8">
         <v>7</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="7">
         <v>4</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
+        <v>15</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>20</v>
+      </c>
+      <c r="B10" s="8">
+        <v>2</v>
+      </c>
+      <c r="C10" s="8">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
+        <v>21</v>
+      </c>
+      <c r="B11" s="8">
+        <v>2</v>
+      </c>
+      <c r="C11" s="8">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="8">
-        <v>1</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
-        <v>100</v>
-      </c>
-      <c r="B10" s="16">
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>22</v>
+      </c>
+      <c r="B12" s="8">
         <v>2</v>
       </c>
-      <c r="C10" s="16">
-        <v>3</v>
-      </c>
-      <c r="D10" s="15">
-        <v>1</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="G12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
+        <v>23</v>
+      </c>
+      <c r="B13" s="8">
+        <v>2</v>
+      </c>
+      <c r="C13" s="8">
         <v>6</v>
       </c>
-      <c r="G10" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
-        <v>101</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="D13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>24</v>
+      </c>
+      <c r="B14" s="8">
         <v>2</v>
       </c>
-      <c r="C11" s="16">
-        <v>4</v>
-      </c>
-      <c r="D11" s="15">
-        <v>1</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="16" t="s">
+      <c r="C14" s="8">
         <v>7</v>
       </c>
-      <c r="G11" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
-        <v>102</v>
-      </c>
-      <c r="B12" s="16">
+      <c r="D14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="7">
         <v>2</v>
       </c>
-      <c r="C12" s="16">
-        <v>5</v>
-      </c>
-      <c r="D12" s="15">
-        <v>1</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
-        <v>103</v>
-      </c>
-      <c r="B13" s="16">
+      <c r="F14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
+        <v>25</v>
+      </c>
+      <c r="B15" s="8">
         <v>2</v>
       </c>
-      <c r="C13" s="16">
-        <v>6</v>
-      </c>
-      <c r="D13" s="15">
-        <v>1</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
-        <v>104</v>
-      </c>
-      <c r="B14" s="16">
-        <v>2</v>
-      </c>
-      <c r="C14" s="16">
-        <v>7</v>
-      </c>
-      <c r="D14" s="15">
-        <v>2</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="16">
-        <v>0</v>
+      <c r="C15" s="8">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EF307C-1311-4A9C-9E1A-2040B03E9272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8626D4-E233-42D0-A289-03841CFB1A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20520" yWindow="4140" windowWidth="19995" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2415" yWindow="2505" windowWidth="19995" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -137,10 +137,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>防御塔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Atk</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -223,19 +219,6 @@
   </si>
   <si>
     <t>坦克工厂</t>
-  </si>
-  <si>
-    <t>122,0,122</t>
-  </si>
-  <si>
-    <t>122,0,117</t>
-  </si>
-  <si>
-    <t>117,0,122</t>
-  </si>
-  <si>
-    <t>112,0,122</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CampID</t>
@@ -261,10 +244,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>109,0,112;112,0,109</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>可以建造的单位列表</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -362,6 +341,30 @@
   <si>
     <t>Images/MainBase</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,0,105;115,0,105;105,0,115;115,0,115</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,110</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>120,0,120</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>120,0,110;110,0,120</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>120,0,100</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,120</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +434,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,7 +484,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -506,9 +515,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -521,8 +527,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -816,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>8</v>
@@ -828,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>22</v>
@@ -837,19 +855,19 @@
         <v>20</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -901,10 +919,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -916,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
@@ -925,19 +943,19 @@
         <v>21</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -991,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
@@ -1016,7 +1034,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N5" s="2"/>
     </row>
@@ -1056,10 +1074,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1101,7 +1119,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1138,14 +1156,14 @@
       <c r="K8" s="4">
         <v>5</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1182,14 +1200,14 @@
       <c r="K9" s="6">
         <v>10</v>
       </c>
-      <c r="L9" s="12" t="s">
-        <v>60</v>
+      <c r="L9" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1228,10 +1246,10 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1269,7 @@
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="21.75" customWidth="1"/>
     <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1260,25 +1278,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1312,180 +1330,180 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
+        <v>10</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16">
+        <v>3</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>4</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="15">
+        <v>2</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>5</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>10</v>
-      </c>
-      <c r="B4" s="8">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="H6" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1</v>
+      </c>
+      <c r="C7" s="16">
+        <v>6</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="15">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
+        <v>14</v>
+      </c>
+      <c r="B8" s="16">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16">
+        <v>7</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="15">
+        <v>4</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
+        <v>15</v>
+      </c>
+      <c r="B9" s="16">
+        <v>1</v>
+      </c>
+      <c r="C9" s="16">
+        <v>1</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>11</v>
-      </c>
-      <c r="B5" s="8">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>12</v>
-      </c>
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>13</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>14</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="8">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="7">
-        <v>4</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>15</v>
-      </c>
-      <c r="B9" s="8">
-        <v>1</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="E9" s="15">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="16">
         <v>1</v>
       </c>
     </row>
@@ -1500,16 +1518,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E10" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>50</v>
+      <c r="F10" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H10" s="8">
         <v>1</v>
@@ -1526,13 +1544,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>51</v>
+        <v>2</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>81</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>6</v>
@@ -1552,16 +1570,16 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E12" s="7">
         <v>1</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>52</v>
+      <c r="F12" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12" s="8">
         <v>1</v>
@@ -1578,22 +1596,22 @@
         <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E13" s="7">
         <v>1</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>53</v>
+      <c r="F13" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>24</v>
       </c>
@@ -1604,16 +1622,16 @@
         <v>7</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7">
-        <v>2</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="H14" s="8">
         <v>1</v>
@@ -1630,16 +1648,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E15" s="7">
         <v>1</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>70</v>
+      <c r="F15" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H15" s="8">
         <v>1</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8626D4-E233-42D0-A289-03841CFB1A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC037EA6-F259-484E-814E-B599B54DD4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="2505" windowWidth="19995" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="3075" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
   <si>
     <t>ID</t>
   </si>
@@ -365,6 +365,22 @@
   <si>
     <t>100,0,120</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildPrefab</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>建造模型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Building</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TowerBuilding</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -809,24 +825,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
     <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.625" customWidth="1"/>
-    <col min="14" max="14" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.25" customWidth="1"/>
+    <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.625" customWidth="1"/>
+    <col min="15" max="15" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -839,38 +856,41 @@
       <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -883,8 +903,8 @@
       <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>17</v>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>17</v>
@@ -905,16 +925,19 @@
         <v>17</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -927,38 +950,41 @@
       <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -971,34 +997,37 @@
       <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="6">
         <v>5</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>3000</v>
       </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
       <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
       <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
         <v>2000</v>
       </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1011,8 +1040,8 @@
       <c r="D5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
+      <c r="E5" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -1032,13 +1061,16 @@
       <c r="K5" s="6">
         <v>0</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="6" t="s">
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1051,36 +1083,39 @@
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="6">
         <v>5</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>400</v>
       </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
       <c r="H6" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6">
         <v>5</v>
       </c>
       <c r="J6" s="6">
+        <v>5</v>
+      </c>
+      <c r="K6" s="6">
         <v>800</v>
       </c>
-      <c r="K6" s="6">
+      <c r="L6" s="6">
         <v>5</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="2"/>
+      <c r="N6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="O6" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1093,36 +1128,39 @@
       <c r="D7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="6">
         <v>5</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>400</v>
       </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
       <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
         <v>5</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J7" s="6">
         <v>8</v>
       </c>
-      <c r="J7" s="6">
+      <c r="K7" s="6">
         <v>500</v>
       </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2" t="s">
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1135,38 +1173,41 @@
       <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="4">
         <v>5</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>500</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
       <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
         <v>10</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>4</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>500</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>5</v>
       </c>
-      <c r="L8" s="12">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="12">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="O8" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1179,38 +1220,41 @@
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="6">
         <v>5</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>600</v>
       </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
       <c r="H9" s="6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I9" s="6">
         <v>20</v>
       </c>
       <c r="J9" s="6">
+        <v>20</v>
+      </c>
+      <c r="K9" s="6">
         <v>2000</v>
       </c>
-      <c r="K9" s="6">
+      <c r="L9" s="6">
         <v>10</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="N9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="O9" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1223,32 +1267,35 @@
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="6">
         <v>3</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>800</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>10</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>20</v>
       </c>
-      <c r="I10" s="6">
+      <c r="J10" s="6">
         <v>5</v>
       </c>
-      <c r="J10" s="6">
+      <c r="K10" s="6">
         <v>500</v>
       </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="6" t="s">
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>38</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC037EA6-F259-484E-814E-B599B54DD4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9999F6EE-E1D7-461B-88EC-6627E2B933F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="3075" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13500" yWindow="2835" windowWidth="25005" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -380,6 +380,10 @@
   </si>
   <si>
     <t>TowerBuilding</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有主基地才能建造其他建筑</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -840,7 +844,7 @@
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.625" customWidth="1"/>
-    <col min="15" max="15" width="19.25" customWidth="1"/>
+    <col min="15" max="15" width="26.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
@@ -1013,7 +1017,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="6">
         <v>2000</v>
@@ -1025,7 +1029,9 @@
       <c r="N4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
@@ -1289,7 +1295,7 @@
         <v>500</v>
       </c>
       <c r="L10" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="6" t="s">

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9999F6EE-E1D7-461B-88EC-6627E2B933F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F66A06-C745-4389-8576-77937EFB6C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13500" yWindow="2835" windowWidth="25005" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1008,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="6">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H4" s="6">
         <v>0</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F66A06-C745-4389-8576-77937EFB6C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2709652-A259-4022-9812-E4AD7241D0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13500" yWindow="2835" windowWidth="25005" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12465" yWindow="3420" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="91">
   <si>
     <t>ID</t>
   </si>
@@ -384,6 +384,14 @@
   </si>
   <si>
     <t>拥有主基地才能建造其他建筑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加电力</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProducePower</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +512,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -561,6 +569,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -829,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
@@ -841,13 +852,14 @@
     <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.625" customWidth="1"/>
-    <col min="15" max="15" width="26.625" customWidth="1"/>
+    <col min="12" max="12" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.625" customWidth="1"/>
+    <col min="16" max="16" width="26.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -881,20 +893,23 @@
       <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -928,20 +943,23 @@
       <c r="K2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -975,20 +993,23 @@
       <c r="K3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1025,15 +1046,18 @@
       <c r="L4" s="6">
         <v>0</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1070,13 +1094,16 @@
       <c r="L5" s="6">
         <v>0</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="6" t="s">
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1111,17 +1138,20 @@
         <v>800</v>
       </c>
       <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
         <v>5</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1156,17 +1186,20 @@
         <v>500</v>
       </c>
       <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1200,20 +1233,23 @@
       <c r="K8" s="4">
         <v>500</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
         <v>5</v>
       </c>
-      <c r="M8" s="12">
-        <v>1</v>
-      </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="12">
+        <v>1</v>
+      </c>
+      <c r="O8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1248,19 +1284,22 @@
         <v>2000</v>
       </c>
       <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
         <v>10</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="O9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="P9" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1295,13 +1334,16 @@
         <v>500</v>
       </c>
       <c r="L10" s="6">
-        <v>2</v>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>38</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2709652-A259-4022-9812-E4AD7241D0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FECC4-DDA4-4E25-98CE-499EC2BE684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12465" yWindow="3420" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,10 +177,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>为基地提供电力支持</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>自动攻击范围内的敌人</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -256,10 +252,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>金钱的来源</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>油田</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -269,14 +261,6 @@
   </si>
   <si>
     <t>碉堡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可生产坦克单位</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可生产步兵单位</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -392,6 +376,22 @@
   </si>
   <si>
     <t>ProducePower</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗5点电力，可生产步兵单位</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗10点电力，可生产坦克单位</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产10点电力，为基地提供电力支持</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>金钱的来源，持续获得金钱</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -856,7 +856,7 @@
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.625" customWidth="1"/>
-    <col min="16" max="16" width="26.625" customWidth="1"/>
+    <col min="16" max="16" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
@@ -873,7 +873,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>16</v>
@@ -894,16 +894,16 @@
         <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>35</v>
@@ -964,7 +964,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>34</v>
@@ -973,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>24</v>
@@ -994,16 +994,16 @@
         <v>31</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>36</v>
@@ -1023,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F4" s="6">
         <v>5</v>
@@ -1054,7 +1054,7 @@
         <v>5</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P5" s="2"/>
     </row>
@@ -1117,7 +1117,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F6" s="6">
         <v>5</v>
@@ -1145,10 +1145,10 @@
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" s="6" t="s">
         <v>56</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -1165,7 +1165,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F7" s="6">
         <v>5</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -1213,7 +1213,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F8" s="4">
         <v>5</v>
@@ -1246,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -1263,7 +1263,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F9" s="6">
         <v>5</v>
@@ -1290,13 +1290,13 @@
         <v>10</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>60</v>
+      <c r="P9" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
@@ -1313,7 +1313,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F10" s="6">
         <v>3</v>
@@ -1341,10 +1341,10 @@
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1373,25 +1373,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1425,25 +1425,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1457,16 +1457,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E4" s="15">
         <v>1</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H4" s="16">
         <v>1</v>
@@ -1483,13 +1483,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E5" s="15">
         <v>2</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>6</v>
@@ -1509,16 +1509,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E6" s="15">
         <v>1</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H6" s="16">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E7" s="15">
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7" s="16">
         <v>1</v>
@@ -1561,16 +1561,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E8" s="15">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H8" s="16">
         <v>1</v>
@@ -1587,16 +1587,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E9" s="15">
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H9" s="16">
         <v>1</v>
@@ -1613,16 +1613,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E10" s="7">
         <v>1</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H10" s="8">
         <v>1</v>
@@ -1639,13 +1639,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E11" s="7">
         <v>2</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>6</v>
@@ -1665,16 +1665,16 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E12" s="7">
         <v>1</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H12" s="8">
         <v>1</v>
@@ -1691,16 +1691,16 @@
         <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E13" s="7">
         <v>1</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
@@ -1717,16 +1717,16 @@
         <v>7</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E14" s="7">
         <v>4</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H14" s="8">
         <v>1</v>
@@ -1743,16 +1743,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E15" s="7">
         <v>1</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H15" s="8">
         <v>1</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FECC4-DDA4-4E25-98CE-499EC2BE684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2611538-EB1E-4002-B3E0-5EAC4E8E7CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12465" yWindow="3420" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="3885" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -134,14 +134,6 @@
   </si>
   <si>
     <t>Tower</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Atk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -392,6 +384,40 @@
   </si>
   <si>
     <t>金钱的来源，持续获得金钱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹类型
+（指向ConfProjectile表）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkInterval</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击频率
+10000=1秒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -840,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
@@ -848,18 +874,20 @@
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.625" customWidth="1"/>
-    <col min="16" max="16" width="33.625" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.625" customWidth="1"/>
+    <col min="19" max="19" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -867,13 +895,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>16</v>
@@ -881,35 +909,44 @@
       <c r="G1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>38</v>
+      <c r="O1" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -934,46 +971,55 @@
       <c r="H2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>24</v>
@@ -981,35 +1027,44 @@
       <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1023,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F4" s="6">
         <v>5</v>
@@ -1034,30 +1089,39 @@
       <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="M4" s="6">
         <v>2</v>
       </c>
-      <c r="K4" s="6">
+      <c r="N4" s="6">
         <v>2000</v>
       </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="S4" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1068,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -1082,13 +1146,13 @@
       <c r="H5" s="6">
         <v>0</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
         <v>0</v>
       </c>
       <c r="L5" s="6">
@@ -1097,13 +1161,22 @@
       <c r="M5" s="6">
         <v>0</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1117,7 +1190,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F6" s="6">
         <v>5</v>
@@ -1128,30 +1201,39 @@
       <c r="H6" s="6">
         <v>0</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
         <v>5</v>
-      </c>
-      <c r="J6" s="6">
-        <v>5</v>
-      </c>
-      <c r="K6" s="6">
-        <v>800</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
       </c>
       <c r="M6" s="6">
         <v>5</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N6" s="6">
+        <v>800</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1165,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F7" s="6">
         <v>5</v>
@@ -1176,30 +1258,39 @@
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
         <v>5</v>
       </c>
-      <c r="J7" s="6">
+      <c r="M7" s="6">
         <v>8</v>
       </c>
-      <c r="K7" s="6">
+      <c r="N7" s="6">
         <v>500</v>
       </c>
-      <c r="L7" s="6">
+      <c r="O7" s="6">
         <v>10</v>
       </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="S7" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1213,7 +1304,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F8" s="4">
         <v>5</v>
@@ -1224,32 +1315,41 @@
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
         <v>10</v>
       </c>
-      <c r="J8" s="4">
+      <c r="M8" s="4">
         <v>4</v>
       </c>
-      <c r="K8" s="4">
+      <c r="N8" s="4">
         <v>500</v>
       </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
         <v>5</v>
       </c>
-      <c r="N8" s="12">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4" t="s">
+      <c r="Q8" s="12">
+        <v>1</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="S8" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1263,7 +1363,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F9" s="6">
         <v>5</v>
@@ -1274,32 +1374,41 @@
       <c r="H9" s="6">
         <v>0</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
         <v>20</v>
       </c>
-      <c r="J9" s="6">
+      <c r="M9" s="6">
         <v>20</v>
       </c>
-      <c r="K9" s="6">
+      <c r="N9" s="6">
         <v>2000</v>
       </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
         <v>10</v>
       </c>
-      <c r="N9" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="6" t="s">
+      <c r="Q9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="S9" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1313,38 +1422,47 @@
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F10" s="6">
         <v>3</v>
       </c>
       <c r="G10" s="6">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="H10" s="6">
-        <v>10</v>
-      </c>
-      <c r="I10" s="6">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2">
+        <v>2000</v>
+      </c>
+      <c r="K10" s="2">
+        <v>4</v>
+      </c>
+      <c r="L10" s="6">
         <v>20</v>
       </c>
-      <c r="J10" s="6">
+      <c r="M10" s="6">
         <v>5</v>
       </c>
-      <c r="K10" s="6">
+      <c r="N10" s="6">
         <v>500</v>
       </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>37</v>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1373,25 +1491,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1425,25 +1543,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>43</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1457,16 +1575,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" s="15">
         <v>1</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H4" s="16">
         <v>1</v>
@@ -1483,13 +1601,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" s="15">
         <v>2</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>6</v>
@@ -1509,16 +1627,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" s="15">
         <v>1</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H6" s="16">
         <v>1</v>
@@ -1535,16 +1653,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" s="15">
         <v>1</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H7" s="16">
         <v>1</v>
@@ -1561,16 +1679,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E8" s="15">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H8" s="16">
         <v>1</v>
@@ -1587,16 +1705,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9" s="15">
         <v>1</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H9" s="16">
         <v>1</v>
@@ -1613,16 +1731,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" s="7">
         <v>1</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H10" s="8">
         <v>1</v>
@@ -1639,13 +1757,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E11" s="7">
         <v>2</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>6</v>
@@ -1665,16 +1783,16 @@
         <v>5</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E12" s="7">
         <v>1</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H12" s="8">
         <v>1</v>
@@ -1691,16 +1809,16 @@
         <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" s="7">
         <v>1</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
@@ -1717,16 +1835,16 @@
         <v>7</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E14" s="7">
         <v>4</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H14" s="8">
         <v>1</v>
@@ -1743,16 +1861,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="G15" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H15" s="8">
         <v>1</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2611538-EB1E-4002-B3E0-5EAC4E8E7CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515A7DCF-8545-4DE3-B07E-69117F16B028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="3885" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10575" yWindow="3480" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -1604,7 +1604,7 @@
         <v>66</v>
       </c>
       <c r="E5" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>60</v>
@@ -1760,7 +1760,7 @@
         <v>66</v>
       </c>
       <c r="E11" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>75</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515A7DCF-8545-4DE3-B07E-69117F16B028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031354EB-D3E9-48B3-952A-565D0096DFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10575" yWindow="3480" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3525" yWindow="1425" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -418,6 +418,14 @@
   </si>
   <si>
     <t>攻击范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoHeal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动回血万分比</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -866,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
@@ -874,20 +882,21 @@
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.625" customWidth="1"/>
-    <col min="19" max="19" width="33.625" customWidth="1"/>
+    <col min="8" max="8" width="10.875" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.625" customWidth="1"/>
+    <col min="20" max="20" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,43 +919,46 @@
         <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -968,10 +980,10 @@
       <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -980,7 +992,7 @@
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -989,23 +1001,26 @@
       <c r="N2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="Q2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1028,43 +1043,46 @@
         <v>19</v>
       </c>
       <c r="H3" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="J3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="L3" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="P3" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1087,9 +1105,9 @@
         <v>5000</v>
       </c>
       <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
+        <v>300</v>
+      </c>
+      <c r="I4" s="6">
         <v>0</v>
       </c>
       <c r="J4" s="2">
@@ -1098,30 +1116,33 @@
       <c r="K4" s="2">
         <v>0</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
         <v>10</v>
       </c>
-      <c r="M4" s="6">
+      <c r="N4" s="6">
         <v>2</v>
       </c>
-      <c r="N4" s="6">
+      <c r="O4" s="6">
         <v>2000</v>
       </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
       <c r="P4" s="6">
         <v>0</v>
       </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="s">
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1144,9 +1165,9 @@
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
+        <v>300</v>
+      </c>
+      <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="2">
@@ -1155,7 +1176,7 @@
       <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="2">
         <v>0</v>
       </c>
       <c r="M5" s="6">
@@ -1170,13 +1191,16 @@
       <c r="P5" s="6">
         <v>0</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="6" t="s">
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1199,9 +1223,9 @@
         <v>400</v>
       </c>
       <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
+        <v>300</v>
+      </c>
+      <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="2">
@@ -1210,30 +1234,33 @@
       <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="L6" s="6">
-        <v>5</v>
+      <c r="L6" s="2">
+        <v>0</v>
       </c>
       <c r="M6" s="6">
         <v>5</v>
       </c>
       <c r="N6" s="6">
+        <v>5</v>
+      </c>
+      <c r="O6" s="6">
         <v>800</v>
       </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
       <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="6" t="s">
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1256,9 +1283,9 @@
         <v>400</v>
       </c>
       <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
+        <v>300</v>
+      </c>
+      <c r="I7" s="6">
         <v>0</v>
       </c>
       <c r="J7" s="2">
@@ -1267,30 +1294,33 @@
       <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
         <v>5</v>
       </c>
-      <c r="M7" s="6">
+      <c r="N7" s="6">
         <v>8</v>
       </c>
-      <c r="N7" s="6">
+      <c r="O7" s="6">
         <v>500</v>
       </c>
-      <c r="O7" s="6">
+      <c r="P7" s="6">
         <v>10</v>
       </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="s">
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1312,10 +1342,10 @@
       <c r="G8" s="4">
         <v>500</v>
       </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="H8" s="6">
+        <v>300</v>
+      </c>
+      <c r="I8" s="4">
         <v>0</v>
       </c>
       <c r="J8" s="2">
@@ -1324,32 +1354,35 @@
       <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
         <v>10</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>4</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="4">
         <v>500</v>
       </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
+      <c r="P8" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
         <v>5</v>
       </c>
-      <c r="Q8" s="12">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4" t="s">
+      <c r="R8" s="12">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1372,9 +1405,9 @@
         <v>600</v>
       </c>
       <c r="H9" s="6">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
+        <v>300</v>
+      </c>
+      <c r="I9" s="6">
         <v>0</v>
       </c>
       <c r="J9" s="2">
@@ -1383,32 +1416,35 @@
       <c r="K9" s="2">
         <v>0</v>
       </c>
-      <c r="L9" s="6">
-        <v>20</v>
+      <c r="L9" s="2">
+        <v>0</v>
       </c>
       <c r="M9" s="6">
         <v>20</v>
       </c>
       <c r="N9" s="6">
+        <v>20</v>
+      </c>
+      <c r="O9" s="6">
         <v>2000</v>
       </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
       <c r="P9" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
         <v>10</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="R9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1431,37 +1467,40 @@
         <v>2000</v>
       </c>
       <c r="H10" s="6">
+        <v>300</v>
+      </c>
+      <c r="I10" s="6">
         <v>4</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>15</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <v>2000</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <v>4</v>
       </c>
-      <c r="L10" s="6">
+      <c r="M10" s="6">
         <v>20</v>
       </c>
-      <c r="M10" s="6">
+      <c r="N10" s="6">
         <v>5</v>
       </c>
-      <c r="N10" s="6">
+      <c r="O10" s="6">
         <v>500</v>
       </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
       <c r="P10" s="6">
         <v>0</v>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="6" t="s">
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2"/>
+      <c r="S10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>35</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031354EB-D3E9-48B3-952A-565D0096DFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586E2E8C-2E0A-4F3E-AC06-C692BCD9442B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3525" yWindow="1425" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13410" yWindow="4650" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -1464,7 +1464,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="6">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H10" s="6">
         <v>300</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586E2E8C-2E0A-4F3E-AC06-C692BCD9442B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19036B0-F2F0-4AE9-9A7C-64C9C1FA06C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13410" yWindow="4650" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
         <v>5000</v>
       </c>
       <c r="H4" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>400</v>
       </c>
       <c r="H6" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>400</v>
       </c>
       <c r="H7" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I7" s="6">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>600</v>
       </c>
       <c r="H9" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I9" s="6">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>1500</v>
       </c>
       <c r="H10" s="6">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I10" s="6">
         <v>4</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19036B0-F2F0-4AE9-9A7C-64C9C1FA06C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA43AF0-2359-4603-88FF-98E65526C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13410" yWindow="4650" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7380" yWindow="3315" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -1721,7 +1721,7 @@
         <v>69</v>
       </c>
       <c r="E8" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>61</v>
@@ -1877,7 +1877,7 @@
         <v>69</v>
       </c>
       <c r="E14" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>72</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA43AF0-2359-4603-88FF-98E65526C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3088B54-76C1-4394-96A1-695C72A08EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="3315" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5640" yWindow="2835" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -193,10 +193,6 @@
   </si>
   <si>
     <t>位置</t>
-  </si>
-  <si>
-    <t>5,0,5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>阵营</t>
@@ -256,10 +252,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>25,0,5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>主基地</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -268,17 +260,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>5,0,25</t>
-  </si>
-  <si>
-    <t>5,0,15;15,0,5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>20,0,20;10,0,20;20,0,10;10,0,10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>OilField</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -319,30 +300,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>105,0,105;115,0,105;105,0,115;115,0,115</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>110,0,110</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>120,0,120</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>120,0,110;110,0,120</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>120,0,100</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,0,120</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>BuildPrefab</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -426,6 +387,62 @@
   </si>
   <si>
     <t>自动回血万分比</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0,25;25,0,15</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0,35</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>35,0,15</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,0,30;20,0,30;30,0,20;20,0,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,0,25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,100;100,0,110</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,90</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>90,0,110</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>95,0,95;105,0,95;95,0,105;105,0,105</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,100</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpOffsetX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>血条X偏移</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpOffsetY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>血条Y偏移</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -495,13 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,7 +563,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -568,12 +585,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -587,10 +598,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -598,14 +615,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
@@ -882,21 +896,23 @@
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.875" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.625" customWidth="1"/>
-    <col min="20" max="20" width="33.625" customWidth="1"/>
+    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.75" customWidth="1"/>
+    <col min="10" max="10" width="10.875" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.625" customWidth="1"/>
+    <col min="22" max="22" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>16</v>
@@ -919,46 +935,52 @@
         <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -983,49 +1005,55 @@
       <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>32</v>
@@ -1034,7 +1062,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>24</v>
@@ -1042,47 +1070,53 @@
       <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="M3" s="3" t="s">
+      <c r="H3" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1096,7 +1130,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F4" s="6">
         <v>5</v>
@@ -1105,44 +1139,50 @@
         <v>5000</v>
       </c>
       <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>140</v>
+      </c>
+      <c r="J4" s="6">
         <v>100</v>
       </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="K4" s="6">
         <v>0</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
         <v>10</v>
       </c>
-      <c r="N4" s="6">
+      <c r="P4" s="6">
         <v>2</v>
       </c>
-      <c r="O4" s="6">
+      <c r="Q4" s="6">
         <v>2000</v>
       </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="V4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1153,10 +1193,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -1165,24 +1205,24 @@
         <v>0</v>
       </c>
       <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>120</v>
+      </c>
+      <c r="J5" s="6">
         <v>100</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
       </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
         <v>0</v>
       </c>
       <c r="O5" s="6">
@@ -1194,13 +1234,19 @@
       <c r="Q5" s="6">
         <v>0</v>
       </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="6" t="s">
-        <v>53</v>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6">
+        <v>0</v>
       </c>
       <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="U5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1214,7 +1260,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F6" s="6">
         <v>5</v>
@@ -1223,44 +1269,50 @@
         <v>400</v>
       </c>
       <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>120</v>
+      </c>
+      <c r="J6" s="6">
         <v>100</v>
       </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="K6" s="6">
         <v>0</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
         <v>5</v>
       </c>
-      <c r="N6" s="6">
+      <c r="P6" s="6">
         <v>5</v>
       </c>
-      <c r="O6" s="6">
+      <c r="Q6" s="6">
         <v>800</v>
       </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1274,7 +1326,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F7" s="6">
         <v>5</v>
@@ -1283,44 +1335,50 @@
         <v>400</v>
       </c>
       <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>120</v>
+      </c>
+      <c r="J7" s="6">
         <v>100</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="6">
         <v>0</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
         <v>5</v>
       </c>
-      <c r="N7" s="6">
+      <c r="P7" s="6">
         <v>8</v>
       </c>
-      <c r="O7" s="6">
+      <c r="Q7" s="6">
         <v>500</v>
       </c>
-      <c r="P7" s="6">
+      <c r="R7" s="6">
         <v>10</v>
       </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2" t="s">
+      <c r="S7" s="6">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="V7" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1334,7 +1392,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F8" s="4">
         <v>5</v>
@@ -1343,46 +1401,52 @@
         <v>500</v>
       </c>
       <c r="H8" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I8" s="6">
+        <v>120</v>
+      </c>
+      <c r="J8" s="6">
         <v>100</v>
       </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="K8" s="4">
         <v>0</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
         <v>10</v>
       </c>
-      <c r="N8" s="4">
+      <c r="P8" s="4">
         <v>4</v>
       </c>
-      <c r="O8" s="4">
+      <c r="Q8" s="4">
         <v>500</v>
       </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
         <v>5</v>
       </c>
-      <c r="R8" s="12">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4" t="s">
+      <c r="T8" s="10">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="V8" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1396,7 +1460,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F9" s="6">
         <v>5</v>
@@ -1405,46 +1469,52 @@
         <v>600</v>
       </c>
       <c r="H9" s="6">
+        <v>-20</v>
+      </c>
+      <c r="I9" s="6">
+        <v>140</v>
+      </c>
+      <c r="J9" s="6">
         <v>100</v>
       </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
+      <c r="K9" s="6">
         <v>0</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
         <v>20</v>
       </c>
-      <c r="N9" s="6">
+      <c r="P9" s="6">
         <v>20</v>
       </c>
-      <c r="O9" s="6">
+      <c r="Q9" s="6">
         <v>2000</v>
       </c>
-      <c r="P9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6">
         <v>10</v>
       </c>
-      <c r="R9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="S9" s="6" t="s">
+      <c r="T9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="V9" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1458,7 +1528,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F10" s="6">
         <v>3</v>
@@ -1467,40 +1537,46 @@
         <v>1500</v>
       </c>
       <c r="H10" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I10" s="6">
+        <v>80</v>
+      </c>
+      <c r="J10" s="6">
         <v>100</v>
       </c>
-      <c r="I10" s="6">
+      <c r="K10" s="6">
         <v>4</v>
       </c>
-      <c r="J10" s="2">
+      <c r="L10" s="2">
         <v>15</v>
       </c>
-      <c r="K10" s="2">
+      <c r="M10" s="2">
         <v>2000</v>
       </c>
-      <c r="L10" s="2">
+      <c r="N10" s="2">
         <v>4</v>
       </c>
-      <c r="M10" s="6">
+      <c r="O10" s="6">
         <v>20</v>
       </c>
-      <c r="N10" s="6">
+      <c r="P10" s="6">
         <v>5</v>
       </c>
-      <c r="O10" s="6">
+      <c r="Q10" s="6">
         <v>500</v>
       </c>
-      <c r="P10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2"/>
-      <c r="S10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="T10" s="2" t="s">
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2"/>
+      <c r="U10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1521,7 +1597,7 @@
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="21.75" customWidth="1"/>
     <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1530,25 +1606,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>40</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1567,7 +1643,7 @@
       <c r="E2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -1582,336 +1658,336 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="11">
         <v>10</v>
       </c>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16">
+      <c r="B4" s="12">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12">
         <v>3</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="15">
-        <v>1</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" s="16">
+      <c r="H4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="A5" s="11">
         <v>11</v>
       </c>
-      <c r="B5" s="16">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16">
+      <c r="B5" s="12">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12">
         <v>4</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="11">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12">
+        <v>5</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>13</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="11">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>15</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="15">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18" t="s">
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
+        <v>20</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2</v>
+      </c>
+      <c r="C10" s="16">
+        <v>3</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="E10" s="15">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
+        <v>21</v>
+      </c>
+      <c r="B11" s="16">
+        <v>2</v>
+      </c>
+      <c r="C11" s="16">
+        <v>4</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="15">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="H11" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15">
+        <v>22</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2</v>
+      </c>
+      <c r="C12" s="16">
         <v>5</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="D12" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="15">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
+        <v>23</v>
+      </c>
+      <c r="B13" s="16">
+        <v>2</v>
+      </c>
+      <c r="C13" s="16">
+        <v>6</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="15">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>1</v>
-      </c>
-      <c r="C7" s="16">
-        <v>6</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="15">
-        <v>1</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
-        <v>14</v>
-      </c>
-      <c r="B8" s="16">
-        <v>1</v>
-      </c>
-      <c r="C8" s="16">
+      <c r="H13" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
+        <v>24</v>
+      </c>
+      <c r="B14" s="16">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16">
         <v>7</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="15">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="15" t="s">
+      <c r="D14" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="15">
+        <v>1</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="15">
+        <v>25</v>
+      </c>
+      <c r="B15" s="16">
+        <v>2</v>
+      </c>
+      <c r="C15" s="16">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="15">
-        <v>15</v>
-      </c>
-      <c r="B9" s="16">
-        <v>1</v>
-      </c>
-      <c r="C9" s="16">
-        <v>1</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="15">
-        <v>1</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>20</v>
-      </c>
-      <c r="B10" s="8">
-        <v>2</v>
-      </c>
-      <c r="C10" s="8">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>21</v>
-      </c>
-      <c r="B11" s="8">
-        <v>2</v>
-      </c>
-      <c r="C11" s="8">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>22</v>
-      </c>
-      <c r="B12" s="8">
-        <v>2</v>
-      </c>
-      <c r="C12" s="8">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>23</v>
-      </c>
-      <c r="B13" s="8">
-        <v>2</v>
-      </c>
-      <c r="C13" s="8">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <v>24</v>
-      </c>
-      <c r="B14" s="8">
-        <v>2</v>
-      </c>
-      <c r="C14" s="8">
-        <v>7</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
-        <v>25</v>
-      </c>
-      <c r="B15" s="8">
-        <v>2</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="H15" s="16">
         <v>1</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3088B54-76C1-4394-96A1-695C72A08EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116DEA09-87EC-4C52-A598-2D803E00675E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="2835" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5985" yWindow="3180" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="R4" s="6">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>5</v>
       </c>
       <c r="P6" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="6">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="R6" s="6">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="P7" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="6">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="R7" s="6">
         <v>10</v>
@@ -1425,10 +1425,10 @@
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="R8" s="6">
         <v>0</v>
@@ -1493,10 +1493,10 @@
         <v>20</v>
       </c>
       <c r="P9" s="6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="R9" s="6">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>20</v>
       </c>
       <c r="P10" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="R10" s="6">
         <v>0</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116DEA09-87EC-4C52-A598-2D803E00675E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6413B9E4-0667-4E28-B95C-22623F66D057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5985" yWindow="3180" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20325" yWindow="2505" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -1552,7 +1552,7 @@
         <v>15</v>
       </c>
       <c r="M10" s="2">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="N10" s="2">
         <v>4</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6413B9E4-0667-4E28-B95C-22623F66D057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB950F-340C-4D43-8E4C-175961CB5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20325" yWindow="2505" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -1552,7 +1552,7 @@
         <v>15</v>
       </c>
       <c r="M10" s="2">
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="N10" s="2">
         <v>4</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB950F-340C-4D43-8E4C-175961CB5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC330B1E-5554-4FB9-B744-029621CBE924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1965" yWindow="4755" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -51,16 +51,6 @@
     <t>编号</t>
   </si>
   <si>
-    <t>主基地</t>
-  </si>
-  <si>
-    <t>电厂</t>
-  </si>
-  <si>
-    <t>兵营</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefab</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -89,10 +79,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>战车工厂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Size</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -169,10 +155,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>自动攻击范围内的敌人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -196,13 +178,6 @@
   </si>
   <si>
     <t>阵营</t>
-  </si>
-  <si>
-    <t>兵营</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>坦克工厂</t>
   </si>
   <si>
     <t>CampID</t>
@@ -232,28 +207,8 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>2,3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>CreateUnitIDList</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>油田</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>油井</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>碉堡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>主基地</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>15,0,15</t>
@@ -292,10 +247,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>油井</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>Images/MainBase</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -320,31 +271,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>拥有主基地才能建造其他建筑</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>增加电力</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ProducePower</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗5点电力，可生产步兵单位</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗10点电力，可生产坦克单位</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>生产10点电力，为基地提供电力支持</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>金钱的来源，持续获得金钱</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -390,10 +321,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>15,0,25;25,0,15</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>15,0,35</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -410,10 +337,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>110,0,100;100,0,110</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>110,0,90</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -443,6 +366,126 @@
   </si>
   <si>
     <t>血条Y偏移</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃取站</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型装甲装配厂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻型载具工场</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>整备营区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础步兵训练与部署中心，用于征召和整编反重装步兵。配备轻武器库、战术模拟室和快速补给通道，支持步兵单位高效投入战场。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>专用于组装与维护高速轻型装甲车辆的制造设施。采用模块化生产线，可快速批量生产獾式坦克，并提供战场损伤修复服务。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大型工业化厂房，拥有重型吊装设备与复合装甲压制线，专门用于制造和升级重装坦克。结构坚固，具备一定防御能力，通常部署于战线后方。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前线指挥枢纽</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>战区核心指挥与部署中心，具备通信中继、单位调度和战场感知能力。所有其他作战建筑必须在其控制范围内建造。被摧毁则丧失作战能力。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源回收站</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过回收战场残骸、处理废弃装备及协调后勤物流获取作战资金。可升级以提升资源转化效率，是经济运转的核心节点。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>模块化动力阵列</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供基地所需能源的分布式发电系统，采用混合能源（柴油、燃料电池或小型燃气轮机）。若电力不足，高级建筑将无法运作或生产速度下降。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>复合防御哨塔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多用途自动防御工事，配备360°旋转炮塔，可切换高爆弹（对步兵）或穿甲弹（对轻型载具）模式。对重装坦克效果有限，需配合其他单位协同防御。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>废弃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源回收站</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>前线指挥枢纽</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>模块化动力阵列</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>整备营区</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型装甲装配厂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻型载具工场</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,0,15</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0,25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/LightVehicleFactory</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,110</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,100</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightVehicleFactory</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -503,7 +546,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,6 +562,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,7 +612,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -591,9 +640,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -620,6 +666,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -888,11 +952,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
@@ -909,7 +973,7 @@
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17.875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.625" customWidth="1"/>
-    <col min="22" max="22" width="33.625" customWidth="1"/>
+    <col min="22" max="22" width="39.625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" x14ac:dyDescent="0.25">
@@ -920,132 +984,132 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>33</v>
+      <c r="V1" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>9</v>
+      <c r="V2" s="13" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -1053,70 +1117,70 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="S3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:22" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1127,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F4" s="6">
         <v>5</v>
@@ -1166,7 +1230,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="6">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="R4" s="6">
         <v>0</v>
@@ -1176,10 +1240,10 @@
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
+      </c>
+      <c r="V4" s="18" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -1192,61 +1256,63 @@
       <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
+      <c r="F5" s="22">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22">
         <v>120</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="22">
         <v>100</v>
       </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K5" s="22">
+        <v>0</v>
+      </c>
+      <c r="L5" s="21">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21">
+        <v>0</v>
+      </c>
+      <c r="O5" s="22">
+        <v>0</v>
+      </c>
+      <c r="P5" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="22">
+        <v>0</v>
+      </c>
+      <c r="R5" s="22">
+        <v>0</v>
+      </c>
+      <c r="S5" s="22">
+        <v>0</v>
+      </c>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="V5" s="23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1257,10 +1323,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F6" s="6">
         <v>5</v>
@@ -1305,14 +1371,14 @@
         <v>0</v>
       </c>
       <c r="T6" s="2"/>
-      <c r="U6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="U6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V6" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1323,10 +1389,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F7" s="6">
         <v>5</v>
@@ -1372,13 +1438,13 @@
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="V7" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1389,10 +1455,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F8" s="4">
         <v>5</v>
@@ -1436,17 +1502,17 @@
       <c r="S8" s="4">
         <v>5</v>
       </c>
-      <c r="T8" s="10">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="T8" s="9">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="V8" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1457,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F9" s="6">
         <v>5</v>
@@ -1493,28 +1559,28 @@
         <v>20</v>
       </c>
       <c r="P9" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="6">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="R9" s="6">
         <v>0</v>
       </c>
       <c r="S9" s="6">
-        <v>10</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="U9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="T9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="V9" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="66" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1522,62 +1588,130 @@
         <v>7</v>
       </c>
       <c r="C10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F10" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="6">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="H10" s="6">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="I10" s="6">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="J10" s="6">
         <v>100</v>
       </c>
       <c r="K10" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O10" s="6">
         <v>20</v>
       </c>
       <c r="P10" s="6">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>800</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>5</v>
+      </c>
+      <c r="T10" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V10" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="66" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="6">
         <v>3</v>
       </c>
-      <c r="Q10" s="6">
-        <v>300</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2"/>
-      <c r="U10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>35</v>
+      <c r="G11" s="6">
+        <v>1500</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I11" s="6">
+        <v>80</v>
+      </c>
+      <c r="J11" s="6">
+        <v>100</v>
+      </c>
+      <c r="K11" s="6">
+        <v>4</v>
+      </c>
+      <c r="L11" s="2">
+        <v>15</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5000</v>
+      </c>
+      <c r="N11" s="2">
+        <v>4</v>
+      </c>
+      <c r="O11" s="6">
+        <v>20</v>
+      </c>
+      <c r="P11" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>400</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="V11" s="18" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1589,16 +1723,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EAF20F-3871-496D-B5D3-5055E4F35A32}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="28.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1606,30 +1740,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -1638,10 +1772,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>2</v>
@@ -1650,7 +1784,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="120" x14ac:dyDescent="0.25">
@@ -1658,336 +1792,388 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>10</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
-        <v>10</v>
-      </c>
-      <c r="B4" s="12">
-        <v>1</v>
-      </c>
-      <c r="C4" s="12">
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>11</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
+        <v>12</v>
+      </c>
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>13</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>6</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>14</v>
+      </c>
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>15</v>
+      </c>
+      <c r="B9" s="11">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>16</v>
+      </c>
+      <c r="B10" s="11">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>20</v>
+      </c>
+      <c r="B11" s="15">
+        <v>2</v>
+      </c>
+      <c r="C11" s="15">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="11">
-        <v>1</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
-        <v>11</v>
-      </c>
-      <c r="B5" s="12">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="D11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>21</v>
+      </c>
+      <c r="B12" s="15">
+        <v>2</v>
+      </c>
+      <c r="C12" s="15">
         <v>4</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="11">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="12" t="s">
+      <c r="D12" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>22</v>
+      </c>
+      <c r="B13" s="15">
+        <v>2</v>
+      </c>
+      <c r="C13" s="15">
+        <v>5</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>23</v>
+      </c>
+      <c r="B14" s="15">
+        <v>2</v>
+      </c>
+      <c r="C14" s="15">
         <v>6</v>
       </c>
-      <c r="H5" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12">
-        <v>5</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="11">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
-        <v>13</v>
-      </c>
-      <c r="B7" s="12">
-        <v>1</v>
-      </c>
-      <c r="C7" s="12">
-        <v>6</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="11">
-        <v>1</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12">
-        <v>1</v>
-      </c>
-      <c r="C8" s="12">
+      <c r="D14" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>24</v>
+      </c>
+      <c r="B15" s="15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="15">
         <v>7</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="11">
-        <v>1</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
-        <v>15</v>
-      </c>
-      <c r="B9" s="12">
-        <v>1</v>
-      </c>
-      <c r="C9" s="12">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="11">
-        <v>1</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
-        <v>20</v>
-      </c>
-      <c r="B10" s="16">
+      <c r="D15" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="14">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>25</v>
+      </c>
+      <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C10" s="16">
-        <v>3</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="15">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
-        <v>21</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="C16" s="15">
+        <v>8</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="14">
+        <v>1</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>26</v>
+      </c>
+      <c r="B17" s="15">
         <v>2</v>
       </c>
-      <c r="C11" s="16">
-        <v>4</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="15">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
-        <v>22</v>
-      </c>
-      <c r="B12" s="16">
-        <v>2</v>
-      </c>
-      <c r="C12" s="16">
-        <v>5</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="15">
-        <v>1</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
-        <v>23</v>
-      </c>
-      <c r="B13" s="16">
-        <v>2</v>
-      </c>
-      <c r="C13" s="16">
-        <v>6</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="15">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
-        <v>24</v>
-      </c>
-      <c r="B14" s="16">
-        <v>2</v>
-      </c>
-      <c r="C14" s="16">
-        <v>7</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="15">
-        <v>1</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="15">
-        <v>25</v>
-      </c>
-      <c r="B15" s="16">
-        <v>2</v>
-      </c>
-      <c r="C15" s="16">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="15">
-        <v>1</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="16">
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="15">
         <v>1</v>
       </c>
     </row>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC330B1E-5554-4FB9-B744-029621CBE924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A7D6C8-8E2E-4EEE-A0E6-CA3152D8372C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="4755" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13155" yWindow="3180" windowWidth="41340" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -63,22 +63,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>MainBase</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stope</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PowerPlant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>VehicleFactory</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Size</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -112,14 +96,6 @@
   </si>
   <si>
     <t>占地尺寸（直径）建议奇数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Barracks</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tower</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -227,30 +203,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Images/Stope</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Images/PowerPlant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Images/Barracks</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Images/VehicleFactory</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Images/Tower</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Images/MainBase</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>110,0,110</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -473,10 +425,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Images/LightVehicleFactory</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>100,0,110</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -485,7 +433,58 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>LightVehicleFactory</t>
+    <t>CommanderCenter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AntiInfantry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Money</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeavyVehicle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MachineGun</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightVehicle</t>
+  </si>
+  <si>
+    <t>Images/CommanderCenter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Money</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Energy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/AntiInfantry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/LightVehicle</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/HeavyVehicle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/MechineGun</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -984,75 +983,75 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="M1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="5" t="s">
+      <c r="T1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -1061,46 +1060,46 @@
         <v>6</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>6</v>
@@ -1117,67 +1116,67 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="M3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="V3" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="66" x14ac:dyDescent="0.3">
@@ -1190,11 +1189,11 @@
       <c r="C4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>8</v>
+      <c r="D4" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6">
         <v>5</v>
@@ -1240,10 +1239,10 @@
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="V4" s="18" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -1257,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>45</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>57</v>
       </c>
       <c r="F5" s="22">
         <v>0</v>
@@ -1306,10 +1305,10 @@
       </c>
       <c r="T5" s="21"/>
       <c r="U5" s="21" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="V5" s="23" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
@@ -1323,10 +1322,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F6" s="6">
         <v>5</v>
@@ -1372,10 +1371,10 @@
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="V6" s="18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="66" x14ac:dyDescent="0.3">
@@ -1389,10 +1388,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F7" s="6">
         <v>5</v>
@@ -1438,10 +1437,10 @@
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="V7" s="18" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
@@ -1455,10 +1454,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4">
         <v>5</v>
@@ -1506,10 +1505,10 @@
         <v>1</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="V8" s="18" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
@@ -1523,10 +1522,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F9" s="6">
         <v>5</v>
@@ -1571,13 +1570,13 @@
         <v>5</v>
       </c>
       <c r="T9" s="20" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="V9" s="18" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="66" x14ac:dyDescent="0.3">
@@ -1591,10 +1590,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F10" s="6">
         <v>5</v>
@@ -1639,13 +1638,13 @@
         <v>5</v>
       </c>
       <c r="T10" s="20" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="V10" s="18" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="66" x14ac:dyDescent="0.3">
@@ -1659,10 +1658,10 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F11" s="6">
         <v>3</v>
@@ -1708,10 +1707,10 @@
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="V11" s="18" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1740,30 +1739,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -1775,7 +1774,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>2</v>
@@ -1784,7 +1783,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="120" x14ac:dyDescent="0.25">
@@ -1792,25 +1791,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1824,16 +1823,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H4" s="11">
         <v>1</v>
@@ -1850,16 +1849,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H5" s="11">
         <v>1</v>
@@ -1876,16 +1875,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H6" s="11">
         <v>1</v>
@@ -1902,16 +1901,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H7" s="11">
         <v>1</v>
@@ -1928,16 +1927,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="E8" s="10">
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H8" s="11">
         <v>1</v>
@@ -1954,16 +1953,16 @@
         <v>8</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H9" s="11">
         <v>1</v>
@@ -1980,16 +1979,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H10" s="11">
         <v>1</v>
@@ -2006,16 +2005,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H11" s="15">
         <v>1</v>
@@ -2032,16 +2031,16 @@
         <v>4</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H12" s="15">
         <v>1</v>
@@ -2058,16 +2057,16 @@
         <v>5</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="E13" s="14">
         <v>1</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H13" s="15">
         <v>1</v>
@@ -2084,16 +2083,16 @@
         <v>6</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E14" s="14">
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H14" s="15">
         <v>1</v>
@@ -2110,16 +2109,16 @@
         <v>7</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="E15" s="14">
         <v>1</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H15" s="15">
         <v>1</v>
@@ -2136,16 +2135,16 @@
         <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="E16" s="14">
         <v>1</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H16" s="15">
         <v>1</v>
@@ -2162,16 +2161,16 @@
         <v>1</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="E17" s="14">
         <v>1</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H17" s="15">
         <v>1</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A7D6C8-8E2E-4EEE-A0E6-CA3152D8372C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFB1B92-10E1-47D1-BA64-D5F2D46CF75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13155" yWindow="3180" windowWidth="41340" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7890" yWindow="1935" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -215,14 +215,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Building</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TowerBuilding</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>增加电力</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -485,6 +477,19 @@
   </si>
   <si>
     <t>Images/MechineGun</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scale</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放比例万分比
+(10000=1)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NowBuilding</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -611,7 +616,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -683,6 +688,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,31 +959,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
     <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.75" customWidth="1"/>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.625" customWidth="1"/>
-    <col min="22" max="22" width="39.625" style="19" customWidth="1"/>
+    <col min="5" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.625" customWidth="1"/>
+    <col min="23" max="23" width="39.625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -991,59 +999,62 @@
       <c r="E1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="K1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1059,13 +1070,13 @@
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1074,10 +1085,10 @@
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -1086,7 +1097,7 @@
       <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -1095,23 +1106,26 @@
       <c r="Q2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="T2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="W2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1127,59 +1141,62 @@
       <c r="E3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="I3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="K3" s="13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="66" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1190,30 +1207,30 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="6">
+        <v>113</v>
+      </c>
+      <c r="F4" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G4" s="6">
         <v>5</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>5000</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
       <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
         <v>140</v>
       </c>
-      <c r="J4" s="6">
+      <c r="K4" s="6">
         <v>100</v>
       </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="L4" s="6">
         <v>0</v>
       </c>
       <c r="M4" s="2">
@@ -1222,30 +1239,33 @@
       <c r="N4" s="2">
         <v>0</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
         <v>10</v>
       </c>
-      <c r="P4" s="6">
+      <c r="Q4" s="6">
         <v>2</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="R4" s="6">
         <v>1200</v>
       </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
       <c r="S4" s="6">
         <v>0</v>
       </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="V4" s="18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W4" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1258,11 +1278,11 @@
       <c r="D5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="22">
-        <v>0</v>
+      <c r="E5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="2">
+        <v>50000</v>
       </c>
       <c r="G5" s="22">
         <v>0</v>
@@ -1271,15 +1291,15 @@
         <v>0</v>
       </c>
       <c r="I5" s="22">
+        <v>0</v>
+      </c>
+      <c r="J5" s="22">
         <v>120</v>
       </c>
-      <c r="J5" s="22">
+      <c r="K5" s="22">
         <v>100</v>
       </c>
-      <c r="K5" s="22">
-        <v>0</v>
-      </c>
-      <c r="L5" s="21">
+      <c r="L5" s="22">
         <v>0</v>
       </c>
       <c r="M5" s="21">
@@ -1288,7 +1308,7 @@
       <c r="N5" s="21">
         <v>0</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="21">
         <v>0</v>
       </c>
       <c r="P5" s="22">
@@ -1303,15 +1323,18 @@
       <c r="S5" s="22">
         <v>0</v>
       </c>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="V5" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="T5" s="22">
+        <v>0</v>
+      </c>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1322,30 +1345,30 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="6">
+        <v>113</v>
+      </c>
+      <c r="F6" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G6" s="6">
         <v>5</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>400</v>
       </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
       <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
         <v>120</v>
       </c>
-      <c r="J6" s="6">
+      <c r="K6" s="6">
         <v>100</v>
       </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="L6" s="6">
         <v>0</v>
       </c>
       <c r="M6" s="2">
@@ -1354,30 +1377,33 @@
       <c r="N6" s="2">
         <v>0</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
         <v>5</v>
       </c>
-      <c r="P6" s="6">
+      <c r="Q6" s="6">
         <v>3</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="R6" s="6">
         <v>400</v>
       </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
       <c r="S6" s="6">
         <v>0</v>
       </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" s="18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="66" x14ac:dyDescent="0.3">
+      <c r="T6" s="6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W6" s="18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1388,62 +1414,65 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G7" s="6">
+        <v>5</v>
+      </c>
+      <c r="H7" s="6">
+        <v>400</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>120</v>
+      </c>
+      <c r="K7" s="6">
         <v>100</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6">
         <v>5</v>
       </c>
-      <c r="G7" s="6">
-        <v>400</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>120</v>
-      </c>
-      <c r="J7" s="6">
-        <v>100</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>5</v>
-      </c>
-      <c r="P7" s="6">
+      <c r="Q7" s="6">
         <v>4</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="R7" s="6">
         <v>300</v>
       </c>
-      <c r="R7" s="6">
+      <c r="S7" s="6">
         <v>10</v>
       </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="V7" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="T7" s="6">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W7" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1454,30 +1483,30 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="4">
+        <v>113</v>
+      </c>
+      <c r="F8" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G8" s="4">
         <v>5</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="4">
         <v>500</v>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <v>-5</v>
       </c>
-      <c r="I8" s="6">
+      <c r="J8" s="6">
         <v>120</v>
       </c>
-      <c r="J8" s="6">
+      <c r="K8" s="6">
         <v>100</v>
       </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="L8" s="4">
         <v>0</v>
       </c>
       <c r="M8" s="2">
@@ -1486,32 +1515,35 @@
       <c r="N8" s="2">
         <v>0</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
         <v>10</v>
       </c>
-      <c r="P8" s="4">
+      <c r="Q8" s="4">
         <v>2</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="4">
         <v>300</v>
       </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
+      <c r="S8" s="6">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
         <v>5</v>
       </c>
-      <c r="T8" s="9">
-        <v>1</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="V8" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="U8" s="9">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W8" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1522,30 +1554,30 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="6">
+        <v>113</v>
+      </c>
+      <c r="F9" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G9" s="6">
         <v>5</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>600</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>-20</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6">
         <v>140</v>
       </c>
-      <c r="J9" s="6">
+      <c r="K9" s="6">
         <v>100</v>
       </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="L9" s="6">
         <v>0</v>
       </c>
       <c r="M9" s="2">
@@ -1554,32 +1586,35 @@
       <c r="N9" s="2">
         <v>0</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
         <v>20</v>
       </c>
-      <c r="P9" s="6">
+      <c r="Q9" s="6">
         <v>6</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="R9" s="6">
         <v>800</v>
       </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
       <c r="S9" s="6">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6">
         <v>5</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="U9" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="U9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="V9" s="18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="66" x14ac:dyDescent="0.3">
+      <c r="W9" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="66" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1590,30 +1625,30 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="6">
+        <v>113</v>
+      </c>
+      <c r="F10" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G10" s="6">
         <v>5</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>600</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>-20</v>
       </c>
-      <c r="I10" s="6">
+      <c r="J10" s="6">
         <v>140</v>
       </c>
-      <c r="J10" s="6">
+      <c r="K10" s="6">
         <v>100</v>
       </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="L10" s="6">
         <v>0</v>
       </c>
       <c r="M10" s="2">
@@ -1622,32 +1657,35 @@
       <c r="N10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
         <v>20</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>6</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="R10" s="6">
         <v>800</v>
       </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
       <c r="S10" s="6">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6">
         <v>5</v>
       </c>
-      <c r="T10" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="U10" s="2" t="s">
+      <c r="U10" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="V10" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="66" x14ac:dyDescent="0.3">
+      <c r="V10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W10" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="66" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1658,59 +1696,62 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="6">
+        <v>113</v>
+      </c>
+      <c r="F11" s="2">
+        <v>30000</v>
+      </c>
+      <c r="G11" s="6">
         <v>3</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>1500</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>-5</v>
       </c>
-      <c r="I11" s="6">
+      <c r="J11" s="6">
         <v>80</v>
       </c>
-      <c r="J11" s="6">
+      <c r="K11" s="6">
         <v>100</v>
       </c>
-      <c r="K11" s="6">
+      <c r="L11" s="6">
         <v>4</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>15</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>5000</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>4</v>
       </c>
-      <c r="O11" s="6">
+      <c r="P11" s="6">
         <v>20</v>
       </c>
-      <c r="P11" s="6">
+      <c r="Q11" s="6">
         <v>3</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="R11" s="6">
         <v>400</v>
       </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
       <c r="S11" s="6">
         <v>0</v>
       </c>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="V11" s="18" t="s">
-        <v>87</v>
+      <c r="T11" s="6">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="W11" s="18" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1823,7 +1864,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
@@ -1832,7 +1873,7 @@
         <v>38</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H4" s="11">
         <v>1</v>
@@ -1849,16 +1890,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H5" s="11">
         <v>1</v>
@@ -1875,16 +1916,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H6" s="11">
         <v>1</v>
@@ -1901,16 +1942,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H7" s="11">
         <v>1</v>
@@ -1927,16 +1968,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" s="10">
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H8" s="11">
         <v>1</v>
@@ -1953,16 +1994,16 @@
         <v>8</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H9" s="11">
         <v>1</v>
@@ -1979,16 +2020,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H10" s="11">
         <v>1</v>
@@ -2005,7 +2046,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
@@ -2014,7 +2055,7 @@
         <v>42</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H11" s="15">
         <v>1</v>
@@ -2031,16 +2072,16 @@
         <v>4</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H12" s="15">
         <v>1</v>
@@ -2057,16 +2098,16 @@
         <v>5</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E13" s="14">
         <v>1</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H13" s="15">
         <v>1</v>
@@ -2083,16 +2124,16 @@
         <v>6</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14" s="14">
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H14" s="15">
         <v>1</v>
@@ -2109,16 +2150,16 @@
         <v>7</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E15" s="14">
         <v>1</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H15" s="15">
         <v>1</v>
@@ -2135,16 +2176,16 @@
         <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E16" s="14">
         <v>1</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H16" s="15">
         <v>1</v>
@@ -2161,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E17" s="14">
         <v>1</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H17" s="15">
         <v>1</v>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFB1B92-10E1-47D1-BA64-D5F2D46CF75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC3DFBD-7FD5-4B86-926D-8CB426DDCC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7890" yWindow="1935" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,7 +489,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>NowBuilding</t>
+    <t>Building</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>

--- a/config/excel/Building.xlsx
+++ b/config/excel/Building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC3DFBD-7FD5-4B86-926D-8CB426DDCC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF98DA49-2EEF-48E4-8C51-535D5F04A703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7890" yWindow="1935" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8235" yWindow="2280" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfBuilding" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -104,14 +104,6 @@
   </si>
   <si>
     <t>CostPower</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗金钱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗电量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -215,10 +207,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>增加电力</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ProducePower</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -490,6 +478,28 @@
   </si>
   <si>
     <t>Building</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanAttack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以攻击
+0=不攻击
+1=攻击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗能量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加能量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗金币</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -959,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.125" customWidth="1"/>
@@ -969,21 +979,21 @@
     <col min="8" max="8" width="6.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.75" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.625" customWidth="1"/>
-    <col min="23" max="23" width="39.625" style="19" customWidth="1"/>
+    <col min="11" max="12" width="10.875" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.625" customWidth="1"/>
+    <col min="24" max="24" width="39.625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -991,16 +1001,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>8</v>
@@ -1009,52 +1019,55 @@
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="V1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="W1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="X1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1088,10 +1101,10 @@
       <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -1100,7 +1113,7 @@
       <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="5" t="s">
@@ -1109,40 +1122,43 @@
       <c r="R2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="X2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>16</v>
@@ -1151,52 +1167,55 @@
         <v>11</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>51</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="S3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="U3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" ht="66" x14ac:dyDescent="0.3">
+      <c r="X3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1207,10 +1226,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F4" s="2">
         <v>50000</v>
@@ -1233,7 +1252,7 @@
       <c r="L4" s="6">
         <v>0</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="6">
         <v>0</v>
       </c>
       <c r="N4" s="2">
@@ -1242,30 +1261,33 @@
       <c r="O4" s="2">
         <v>0</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
         <v>10</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="R4" s="6">
         <v>2</v>
       </c>
-      <c r="R4" s="6">
+      <c r="S4" s="6">
         <v>1200</v>
       </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
       <c r="T4" s="6">
         <v>0</v>
       </c>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W4" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="U4" s="6">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="X4" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1276,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2">
         <v>50000</v>
@@ -1299,10 +1321,10 @@
       <c r="K5" s="22">
         <v>100</v>
       </c>
-      <c r="L5" s="22">
-        <v>0</v>
-      </c>
-      <c r="M5" s="21">
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="22">
         <v>0</v>
       </c>
       <c r="N5" s="21">
@@ -1311,7 +1333,7 @@
       <c r="O5" s="21">
         <v>0</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="21">
         <v>0</v>
       </c>
       <c r="Q5" s="22">
@@ -1326,15 +1348,18 @@
       <c r="T5" s="22">
         <v>0</v>
       </c>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="W5" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="U5" s="22">
+        <v>0</v>
+      </c>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1345,10 +1370,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F6" s="2">
         <v>50000</v>
@@ -1371,7 +1396,7 @@
       <c r="L6" s="6">
         <v>0</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="6">
         <v>0</v>
       </c>
       <c r="N6" s="2">
@@ -1380,30 +1405,33 @@
       <c r="O6" s="2">
         <v>0</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
         <v>5</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="R6" s="6">
         <v>3</v>
       </c>
-      <c r="R6" s="6">
+      <c r="S6" s="6">
         <v>400</v>
       </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
       <c r="T6" s="6">
         <v>0</v>
       </c>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="W6" s="18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="66" x14ac:dyDescent="0.3">
+      <c r="U6" s="6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="X6" s="18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1414,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F7" s="2">
         <v>50000</v>
@@ -1440,7 +1468,7 @@
       <c r="L7" s="6">
         <v>0</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="6">
         <v>0</v>
       </c>
       <c r="N7" s="2">
@@ -1449,30 +1477,33 @@
       <c r="O7" s="2">
         <v>0</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
         <v>5</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="R7" s="6">
         <v>4</v>
       </c>
-      <c r="R7" s="6">
+      <c r="S7" s="6">
         <v>300</v>
       </c>
-      <c r="S7" s="6">
+      <c r="T7" s="6">
         <v>10</v>
       </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="W7" s="18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="U7" s="6">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1483,10 +1514,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F8" s="2">
         <v>50000</v>
@@ -1506,10 +1537,10 @@
       <c r="K8" s="6">
         <v>100</v>
       </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
         <v>0</v>
       </c>
       <c r="N8" s="2">
@@ -1518,32 +1549,35 @@
       <c r="O8" s="2">
         <v>0</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
         <v>10</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="4">
         <v>2</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>300</v>
       </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
+      <c r="T8" s="6">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
         <v>5</v>
       </c>
-      <c r="U8" s="9">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="W8" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="V8" s="9">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="X8" s="18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1554,10 +1588,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2">
         <v>50000</v>
@@ -1580,7 +1614,7 @@
       <c r="L9" s="6">
         <v>0</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="6">
         <v>0</v>
       </c>
       <c r="N9" s="2">
@@ -1589,32 +1623,35 @@
       <c r="O9" s="2">
         <v>0</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
         <v>20</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="R9" s="6">
         <v>6</v>
       </c>
-      <c r="R9" s="6">
+      <c r="S9" s="6">
         <v>800</v>
       </c>
-      <c r="S9" s="6">
-        <v>0</v>
-      </c>
       <c r="T9" s="6">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
         <v>5</v>
       </c>
-      <c r="U9" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="V9" s="2" t="s">
+      <c r="V9" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X9" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="W9" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="66" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:24" ht="66" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1625,10 +1662,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F10" s="2">
         <v>50000</v>
@@ -1651,7 +1688,7 @@
       <c r="L10" s="6">
         <v>0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="6">
         <v>0</v>
       </c>
       <c r="N10" s="2">
@@ -1660,32 +1697,35 @@
       <c r="O10" s="2">
         <v>0</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6">
         <v>20</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="R10" s="6">
         <v>6</v>
       </c>
-      <c r="R10" s="6">
+      <c r="S10" s="6">
         <v>800</v>
       </c>
-      <c r="S10" s="6">
-        <v>0</v>
-      </c>
       <c r="T10" s="6">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6">
         <v>5</v>
       </c>
-      <c r="U10" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="W10" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="66" x14ac:dyDescent="0.3">
+      <c r="V10" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X10" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="66" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1696,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F11" s="2">
         <v>30000</v>
@@ -1720,38 +1760,41 @@
         <v>100</v>
       </c>
       <c r="L11" s="6">
+        <v>1</v>
+      </c>
+      <c r="M11" s="6">
         <v>4</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>15</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>5000</v>
       </c>
-      <c r="O11" s="2">
-        <v>4</v>
-      </c>
-      <c r="P11" s="6">
+      <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="6">
         <v>20</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="R11" s="6">
         <v>3</v>
       </c>
-      <c r="R11" s="6">
+      <c r="S11" s="6">
         <v>400</v>
       </c>
-      <c r="S11" s="6">
-        <v>0</v>
-      </c>
       <c r="T11" s="6">
         <v>0</v>
       </c>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="W11" s="18" t="s">
-        <v>85</v>
+      <c r="U11" s="6">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="X11" s="18" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1780,25 +1823,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1832,25 +1875,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1864,16 +1907,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H4" s="11">
         <v>1</v>
@@ -1890,16 +1933,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H5" s="11">
         <v>1</v>
@@ -1916,16 +1959,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H6" s="11">
         <v>1</v>
@@ -1942,16 +1985,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H7" s="11">
         <v>1</v>
@@ -1968,16 +2011,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E8" s="10">
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H8" s="11">
         <v>1</v>
@@ -1994,16 +2037,16 @@
         <v>8</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H9" s="11">
         <v>1</v>
@@ -2020,16 +2063,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H10" s="11">
         <v>1</v>
@@ -2046,16 +2089,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H11" s="15">
         <v>1</v>
@@ -2072,16 +2115,16 @@
         <v>4</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H12" s="15">
         <v>1</v>
@@ -2098,16 +2141,16 @@
         <v>5</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E13" s="14">
         <v>1</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H13" s="15">
         <v>1</v>
@@ -2124,16 +2167,16 @@
         <v>6</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E14" s="14">
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H14" s="15">
         <v>1</v>
@@ -2150,16 +2193,16 @@
         <v>7</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E15" s="14">
         <v>1</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H15" s="15">
         <v>1</v>
@@ -2176,16 +2219,16 @@
         <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E16" s="14">
         <v>1</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H16" s="15">
         <v>1</v>
@@ -2202,16 +2245,16 @@
         <v>1</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E17" s="14">
         <v>1</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H17" s="15">
         <v>1</v>
